--- a/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-28T14:55:19+00:00</t>
+    <t>2026-10-29T04:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-annex-81</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-annex-81</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -627,7 +627,7 @@
     <t>validity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-validity-period}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-validity-period}
 </t>
   </si>
   <si>
@@ -647,7 +647,7 @@
     <t>latest</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-ext-latest-end-date}
+    <t xml:space="preserve">Extension {https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-ext-latest-end-date}
 </t>
   </si>
   <si>
@@ -663,7 +663,7 @@
     <t>statusReason</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {request-statusReason|5.3.0}
+    <t xml:space="preserve">Extension {request-statusReason|5.4.0}
 </t>
   </si>
   <si>
@@ -731,10 +731,10 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-prescription-status-reason.html).</t>
-  </si>
-  <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/ValueSet/be-vs-prescription-status-reason</t>
+    <t>The actual valueset will be provided when a terminology package is available. For current guidance, see the included [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-prescription-status-reason.html).</t>
+  </si>
+  <si>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/ValueSet/be-vs-prescription-status-reason</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -893,7 +893,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1016,7 +1016,7 @@
     <t>ServiceRequest.identifier:SHORT.system</t>
   </si>
   <si>
-    <t>https://www.ehealth.fgov.be/standards/fhir/referral/NamingSystem/uhmep-short</t>
+    <t>https://www.ehealth.fgov.be/standards/fhir/drp/NamingSystem/uhmep-short</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:SHORT.value</t>
@@ -1072,7 +1072,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/referral/StructureDefinition/be-annex-81)
+    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/drp/StructureDefinition/be-annex-81)
 </t>
   </si>
   <si>
@@ -1259,7 +1259,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Categories of care that can be prescribed. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-categories-of-care.html).</t>
+    <t>Categories of care that can be prescribed. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-categories-of-care.html).</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
@@ -1282,7 +1282,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Technical type for Annex 81 prescriptions. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-annex81-technical-type.html).</t>
+    <t>Technical type for Annex 81 prescriptions. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-annex81-technical-type.html).</t>
   </si>
   <si>
     <t>ServiceRequest.priority</t>
@@ -2630,7 +2630,7 @@
     <t>ServiceRequest.note.extension.value[x]</t>
   </si>
   <si>
-    <t>Types of notes that can be associated with a prescription. See [ValueSet](https://www.ehealth.fgov.be/standards/fhir/referral/1.0.0/ValueSet-be-vs-note-type.html).</t>
+    <t>Types of notes that can be associated with a prescription. See [ValueSet](https://build.fhir.org/ig/hl7-be/referral-uhmep/ValueSet-be-vs-note-type.html).</t>
   </si>
   <si>
     <t>https://www.ehealth.fgov.be/standards/fhir/terminology/ValueSet/be-vs-note-type</t>
@@ -3075,8 +3075,8 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="186.48046875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.7265625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="177.3515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="71.54296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="62.61328125" customWidth="true" bestFit="true"/>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:33:29+00:00</t>
+    <t>2026-10-29T04:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T04:45:11+00:00</t>
+    <t>2026-10-29T06:41:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:41:01+00:00</t>
+    <t>2026-10-29T06:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T06:43:17+00:00</t>
+    <t>2026-10-29T07:36:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
+++ b/branches/release-3.0.0/StructureDefinition-ereferral-annex-81.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T07:36:53+00:00</t>
+    <t>2026-10-29T08:00:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
